--- a/SGC-CKN/Excel/93c3f964-3328-46e2-83a2-10ccd070faae_Thi_công_cọc_khoan_nhồi_P7-76_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/93c3f964-3328-46e2-83a2-10ccd070faae_Thi_công_cọc_khoan_nhồi_P7-76_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>17:40 19/03/2026</t>
+    <t>07:40 19/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -143,20 +143,24 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">22:14
+    <t xml:space="preserve">23:19
 18/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:09
+19/03/2026</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu KC chặt, lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">00:10
 19/03/2026</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu KC chặt, lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
-  </si>
-  <si>
     <t xml:space="preserve">00:52
 19/03/2026</t>
   </si>
@@ -167,7 +171,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">02:56
+    <t xml:space="preserve">02:35
 19/03/2026</t>
   </si>
   <si>
@@ -175,18 +179,26 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02:36
+19/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:27
+19/03/2026</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:28
 19/03/2026</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">04:00
 19/03/2026</t>
   </si>
@@ -212,7 +224,7 @@
 19/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">05:40
+    <t xml:space="preserve">07:40
 19/03/2026</t>
   </si>
   <si>
@@ -250,7 +262,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -333,6 +345,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -343,7 +361,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,11 +410,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
@@ -412,6 +425,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
@@ -423,6 +441,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -571,35 +594,35 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,13 +651,16 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1293,16 +1319,16 @@
         <v>9.33</v>
       </c>
       <c r="G13" s="12">
-        <v>17.55</v>
+        <v>-17.53</v>
       </c>
       <c r="H13" s="12">
         <v>0.95</v>
       </c>
       <c r="I13" s="12">
-        <v>8.22</v>
+        <v>26.86</v>
       </c>
       <c r="J13" s="8">
-        <v>8.65</v>
+        <v>28.27</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1325,159 +1351,159 @@
         <v>42</v>
       </c>
       <c r="F14" s="15">
-        <v>17.55</v>
+        <v>-17.53</v>
       </c>
       <c r="G14" s="15">
         <v>21.84</v>
       </c>
       <c r="H14" s="15">
-        <v>1.93</v>
+        <v>0.83</v>
       </c>
       <c r="I14" s="15">
-        <v>4.29</v>
-      </c>
-      <c r="J14" s="18">
-        <v>2.22</v>
+        <v>39.37</v>
+      </c>
+      <c r="J14" s="8">
+        <v>47.24</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="19">
+      <c r="E15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="18">
         <v>21.84</v>
       </c>
-      <c r="G15" s="19">
-        <v>25.84</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="G15" s="18">
+        <v>-25.84</v>
+      </c>
+      <c r="H15" s="18">
         <v>0.7</v>
       </c>
-      <c r="I15" s="19">
-        <v>4</v>
+      <c r="I15" s="18">
+        <v>47.68</v>
       </c>
       <c r="J15" s="8">
-        <v>5.71</v>
-      </c>
-      <c r="K15" s="20" t="s">
+        <v>68.11</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="E16" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="21">
+        <v>-25.84</v>
+      </c>
+      <c r="G16" s="21">
+        <v>-36.04</v>
+      </c>
+      <c r="H16" s="21">
+        <v>1.72</v>
+      </c>
+      <c r="I16" s="21">
+        <v>10.2</v>
+      </c>
+      <c r="J16" s="8">
+        <v>5.94</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="22">
-        <v>25.84</v>
-      </c>
-      <c r="G16" s="22">
-        <v>36.04</v>
-      </c>
-      <c r="H16" s="22">
-        <v>2.07</v>
-      </c>
-      <c r="I16" s="22">
-        <v>10.2</v>
-      </c>
-      <c r="J16" s="18">
-        <v>4.94</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="27" t="s">
+      <c r="C17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="25">
-        <v>36.04</v>
-      </c>
-      <c r="G17" s="25">
-        <v>38.14</v>
-      </c>
-      <c r="H17" s="25">
-        <v>0.53</v>
-      </c>
-      <c r="I17" s="25">
-        <v>2.1</v>
-      </c>
-      <c r="J17" s="18">
-        <v>3.94</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="D17" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="24">
+        <v>-36.04</v>
+      </c>
+      <c r="G17" s="24">
+        <v>-38.19</v>
+      </c>
+      <c r="H17" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="I17" s="24">
+        <v>2.15</v>
+      </c>
+      <c r="J17" s="27">
+        <v>2.53</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F18" s="28">
-        <v>38.14</v>
+        <v>-38.19</v>
       </c>
       <c r="G18" s="28">
-        <v>39.7</v>
+        <v>-39.7</v>
       </c>
       <c r="H18" s="28">
         <v>0.53</v>
       </c>
       <c r="I18" s="28">
-        <v>1.56</v>
-      </c>
-      <c r="J18" s="18">
-        <v>2.93</v>
+        <v>1.51</v>
+      </c>
+      <c r="J18" s="27">
+        <v>2.83</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1485,34 +1511,34 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F19" s="31">
-        <v>39.7</v>
+        <v>-39.7</v>
       </c>
       <c r="G19" s="31">
-        <v>44.8</v>
+        <v>-43.95</v>
       </c>
       <c r="H19" s="31">
         <v>1.35</v>
       </c>
       <c r="I19" s="31">
-        <v>5.1</v>
-      </c>
-      <c r="J19" s="18">
-        <v>3.78</v>
+        <v>4.25</v>
+      </c>
+      <c r="J19" s="27">
+        <v>3.15</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1520,53 +1546,53 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F20" s="34">
-        <v>44.8</v>
+        <v>-43.95</v>
       </c>
       <c r="G20" s="34">
-        <v>44.8</v>
+        <v>-44.8</v>
       </c>
       <c r="H20" s="34">
-        <v>0.03</v>
+        <v>2.03</v>
       </c>
       <c r="I20" s="34">
-        <v>0</v>
-      </c>
-      <c r="J20" s="18">
-        <v>0</v>
+        <v>0.85</v>
+      </c>
+      <c r="J20" s="37">
+        <v>0.42</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1661,31 +1687,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,16 +1789,16 @@
         <v>9.33</v>
       </c>
       <c r="F4" s="12">
-        <v>17.55</v>
+        <v>-17.53</v>
       </c>
       <c r="G4" s="12">
         <v>0.95</v>
       </c>
       <c r="H4" s="12">
-        <v>8.22</v>
+        <v>26.86</v>
       </c>
       <c r="I4" s="8">
-        <v>8.65</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,106 +1815,106 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>17.55</v>
+        <v>-17.53</v>
       </c>
       <c r="F5" s="15">
         <v>21.84</v>
       </c>
       <c r="G5" s="15">
-        <v>1.93</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="15">
-        <v>4.29</v>
-      </c>
-      <c r="I5" s="18">
-        <v>2.22</v>
+        <v>39.37</v>
+      </c>
+      <c r="I5" s="8">
+        <v>47.24</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>21.84</v>
       </c>
-      <c r="F6" s="19">
-        <v>25.84</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="18">
+        <v>-25.84</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.7</v>
       </c>
-      <c r="H6" s="19">
-        <v>4</v>
+      <c r="H6" s="18">
+        <v>47.68</v>
       </c>
       <c r="I6" s="8">
-        <v>5.71</v>
+        <v>68.11</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>25.84</v>
-      </c>
-      <c r="F7" s="22">
-        <v>36.04</v>
-      </c>
-      <c r="G7" s="22">
-        <v>2.07</v>
-      </c>
-      <c r="H7" s="22">
+      <c r="E7" s="21">
+        <v>-25.84</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-36.04</v>
+      </c>
+      <c r="G7" s="21">
+        <v>1.72</v>
+      </c>
+      <c r="H7" s="21">
         <v>10.2</v>
       </c>
-      <c r="I7" s="18">
-        <v>4.94</v>
+      <c r="I7" s="8">
+        <v>5.94</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C8" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>36.04</v>
-      </c>
-      <c r="F8" s="25">
-        <v>38.14</v>
-      </c>
-      <c r="G8" s="25">
-        <v>0.53</v>
-      </c>
-      <c r="H8" s="25">
-        <v>2.1</v>
-      </c>
-      <c r="I8" s="18">
-        <v>3.94</v>
+      <c r="E8" s="24">
+        <v>-36.04</v>
+      </c>
+      <c r="F8" s="24">
+        <v>-38.19</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="H8" s="24">
+        <v>2.15</v>
+      </c>
+      <c r="I8" s="27">
+        <v>2.53</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1899,25 +1925,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>38.14</v>
+        <v>-38.19</v>
       </c>
       <c r="F9" s="28">
-        <v>39.7</v>
+        <v>-39.7</v>
       </c>
       <c r="G9" s="28">
         <v>0.53</v>
       </c>
       <c r="H9" s="28">
-        <v>1.56</v>
-      </c>
-      <c r="I9" s="18">
-        <v>2.93</v>
+        <v>1.51</v>
+      </c>
+      <c r="I9" s="27">
+        <v>2.83</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1928,25 +1954,25 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>39.7</v>
+        <v>-39.7</v>
       </c>
       <c r="F10" s="31">
-        <v>44.8</v>
+        <v>-43.95</v>
       </c>
       <c r="G10" s="31">
         <v>1.35</v>
       </c>
       <c r="H10" s="31">
-        <v>5.1</v>
-      </c>
-      <c r="I10" s="18">
-        <v>3.78</v>
+        <v>4.25</v>
+      </c>
+      <c r="I10" s="27">
+        <v>3.15</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1957,54 +1983,54 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>44.8</v>
+        <v>-43.95</v>
       </c>
       <c r="F11" s="34">
-        <v>44.8</v>
+        <v>-44.8</v>
       </c>
       <c r="G11" s="34">
-        <v>0.03</v>
+        <v>2.03</v>
       </c>
       <c r="H11" s="34">
+        <v>0.85</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="40">
+        <v>10</v>
+      </c>
+      <c r="E12" s="40">
         <v>0</v>
       </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>44.8</v>
-      </c>
-      <c r="G12" s="39">
-        <v>9.25</v>
-      </c>
-      <c r="H12" s="39">
-        <v>44.8</v>
-      </c>
-      <c r="I12" s="39">
-        <v>4.84</v>
+      <c r="F12" s="40">
+        <v>-44.8</v>
+      </c>
+      <c r="G12" s="40">
+        <v>10.12</v>
+      </c>
+      <c r="H12" s="40">
+        <v>142.2</v>
+      </c>
+      <c r="I12" s="40">
+        <v>14.06</v>
       </c>
     </row>
   </sheetData>
